--- a/src/performance_dashboard/data/processed/Werknemers_gegevens - Test.xlsx
+++ b/src/performance_dashboard/data/processed/Werknemers_gegevens - Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SharonBuitenweg\Repos\performance_dashboard\src\performance_dashboard\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BEB54C-6021-447C-8169-3966D6B1A302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2F66A6-0986-48CD-87A9-4394B5556CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -416,7 +416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -476,6 +476,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4112,8 +4113,8 @@
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="7"/>
-      <c r="N2" t="s">
-        <v>38</v>
+      <c r="N2" s="29" t="s">
+        <v>67</v>
       </c>
       <c r="O2">
         <v>1001</v>
@@ -4346,7 +4347,7 @@
       <c r="L8" s="28"/>
       <c r="M8" s="9"/>
       <c r="N8" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="O8" s="5">
         <v>1007</v>
@@ -4411,6 +4412,7 @@
       <c r="K12" s="8"/>
       <c r="L12" s="3"/>
       <c r="M12" s="9"/>
+      <c r="N12" s="29"/>
     </row>
     <row r="13" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
@@ -6798,12 +6800,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6945,15 +6944,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{314A3A46-A3C4-4EB8-A142-84075FA7121C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F85D899-E1FF-40CC-BD8D-A28BF92CCF8B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6977,10 +6980,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F85D899-E1FF-40CC-BD8D-A28BF92CCF8B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{314A3A46-A3C4-4EB8-A142-84075FA7121C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>